--- a/data/Mörel-Filet/cost/cost_report.xlsx
+++ b/data/Mörel-Filet/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>169.1036446779111</v>
+        <v>146.9953572308211</v>
       </c>
       <c r="C2" t="n">
-        <v>3386.55197668878</v>
+        <v>3378.970601441749</v>
       </c>
       <c r="D2" t="n">
-        <v>6718.019972524557</v>
+        <v>7764.782775894844</v>
       </c>
       <c r="E2" t="n">
-        <v>1525.845724222225</v>
+        <v>803.3410332313069</v>
       </c>
       <c r="F2" t="n">
-        <v>9453.129537280041</v>
+        <v>8849.929746529491</v>
       </c>
       <c r="G2" t="n">
-        <v>21252.65085539352</v>
+        <v>20944.01951432821</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1428415059553864</v>
+        <v>3.378411822835451</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>169.2359502544074</v>
+        <v>147.0312075520648</v>
       </c>
       <c r="C3" t="n">
-        <v>3393.341798603963</v>
+        <v>3384.677518315459</v>
       </c>
       <c r="D3" t="n">
-        <v>6903.272268404941</v>
+        <v>7939.611493709045</v>
       </c>
       <c r="E3" t="n">
-        <v>1529.790564807089</v>
+        <v>806.7569813161037</v>
       </c>
       <c r="F3" t="n">
-        <v>10045.42319900591</v>
+        <v>9444.308607137815</v>
       </c>
       <c r="G3" t="n">
-        <v>22041.06378107631</v>
+        <v>21722.38580803049</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.148140519729503</v>
+        <v>3.503967563811599</v>
       </c>
     </row>
     <row r="4">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>169.7573104062864</v>
+        <v>146.4564434947356</v>
       </c>
       <c r="C4" t="n">
-        <v>2783.225267299118</v>
+        <v>2905.539354306476</v>
       </c>
       <c r="D4" t="n">
-        <v>11003.88187308651</v>
+        <v>11993.20648938565</v>
       </c>
       <c r="E4" t="n">
-        <v>1517.873914756988</v>
+        <v>802.8950180389087</v>
       </c>
       <c r="F4" t="n">
-        <v>9070.818645542204</v>
+        <v>8247.953929789037</v>
       </c>
       <c r="G4" t="n">
-        <v>24545.5570110911</v>
+        <v>24096.05123501481</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1649735062150263</v>
+        <v>3.88685583110401</v>
       </c>
     </row>
     <row r="5">
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>169.428937972148</v>
+        <v>146.3006800390056</v>
       </c>
       <c r="C5" t="n">
-        <v>2764.4601321721</v>
+        <v>2868.615167270365</v>
       </c>
       <c r="D5" t="n">
-        <v>11047.34436525867</v>
+        <v>12053.18990668963</v>
       </c>
       <c r="E5" t="n">
-        <v>1522.455766013412</v>
+        <v>798.0857879725104</v>
       </c>
       <c r="F5" t="n">
-        <v>8254.083152647923</v>
+        <v>7471.348143249726</v>
       </c>
       <c r="G5" t="n">
-        <v>23757.77235406425</v>
+        <v>23337.53968522124</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1596787151066641</v>
+        <v>3.764502794437541</v>
       </c>
     </row>
   </sheetData>
